--- a/quizzes/sculpture-14e.xlsx
+++ b/quizzes/sculpture-14e.xlsx
@@ -591,7 +591,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>c.1377</t>
+          <t>environ 1377</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -646,12 +646,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>c.1335</t>
+          <t>environ 1335</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>c.1401</t>
+          <t>environ 1401</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -706,12 +706,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>c.1335</t>
+          <t>environ 1335</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>c.1401</t>
+          <t>environ 1401</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>c.1308</t>
+          <t>environ 1308</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -836,7 +836,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>c.1290</t>
+          <t>environ 1290</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>c.1290</t>
+          <t>environ 1290</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -956,7 +956,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>c.1290</t>
+          <t>environ 1290</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1016,7 +1016,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>c.1397</t>
+          <t>environ 1397</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>c.1397</t>
+          <t>environ 1397</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>c.1340</t>
+          <t>environ 1340</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>c.1340</t>
+          <t>environ 1340</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1251,7 +1251,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>c.1340</t>
+          <t>environ 1340</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>c.1290</t>
+          <t>environ 1290</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>c.1340</t>
+          <t>environ 1340</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>c.1248</t>
+          <t>environ 1248</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>c.1315</t>
+          <t>environ 1315</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1491,12 +1491,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>c.1248</t>
+          <t>environ 1248</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>c.1315</t>
+          <t>environ 1315</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>c.1248</t>
+          <t>environ 1248</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>c.1315</t>
+          <t>environ 1315</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1731,7 +1731,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>c.1320</t>
+          <t>environ 1320</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>c.1275</t>
+          <t>environ 1275</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1841,7 +1841,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>c.1320</t>
+          <t>environ 1320</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>c.1280</t>
+          <t>environ 1280</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>c.1280</t>
+          <t>environ 1280</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>c.1280</t>
+          <t>environ 1280</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">

--- a/quizzes/sculpture-14e.xlsx
+++ b/quizzes/sculpture-14e.xlsx
@@ -526,37 +526,42 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/e/eb/Agnolo_di_ventura%2C_portale_della_cappella_petroni%2C_1336%2C_02_madonna_col_bambino_tra_s._francesco_e_il_beato_pietro_da_siena.jpg/1280px-Agnolo_di_ventura%2C_portale_della_cappella_petroni%2C_1336%2C_02_madonna_col_bambino_tra_s._francesco_e_il_beato_pietro_da_siena.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/1f/Alberto_Arnoldi%2C_madonna_col_bambino_tra_i_ss._pietro_martire_e_lucia%2C_post_1351%2C_01.JPG/1280px-Alberto_Arnoldi%2C_madonna_col_bambino_tra_i_ss._pietro_martire_e_lucia%2C_post_1351%2C_01.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Agnolo</t>
+          <t>Alberto</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VENTURA</t>
+          <t>ARNOLDI</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>environ 1377</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>1336</t>
+          <t>1359-1364</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Sienne</t>
+          <t>Florence</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Basilique San Francesco</t>
+          <t>Loggia del Bigallo</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>"Portail de la chapelle Petroni"</t>
+          <t>"Vierge à l'Enfant entre saint Pierre martyr et sainte Lucie"</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -576,42 +581,47 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/1f/Alberto_Arnoldi%2C_madonna_col_bambino_tra_i_ss._pietro_martire_e_lucia%2C_post_1351%2C_01.JPG/1280px-Alberto_Arnoldi%2C_madonna_col_bambino_tra_i_ss._pietro_martire_e_lucia%2C_post_1351%2C_01.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/4/4d/Charles-V-Jeanne-le-Bourbon2.jpg/1280px-Charles-V-Jeanne-le-Bourbon2.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Alberto</t>
+          <t>André</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ARNOLDI</t>
+          <t>BEAUNEVEU</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>environ 1335</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>environ 1377</t>
+          <t>environ 1401</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1359-1364</t>
+          <t>1364</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Florence</t>
+          <t>Saint-Denis</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Loggia del Bigallo</t>
+          <t>Basilique de Saint-Denis</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>"Vierge à l'Enfant entre saint Pierre martyr et sainte Lucie"</t>
+          <t>"Gisant de Charles V"</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -621,7 +631,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>italienne</t>
+          <t>française</t>
         </is>
       </c>
       <c r="U3" t="n">
@@ -631,7 +641,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/4/4d/Charles-V-Jeanne-le-Bourbon2.jpg/1280px-Charles-V-Jeanne-le-Bourbon2.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/2/21/Statue_of_Saint_Catherine_Gravenkapel_Kortrijk_17052015_5.jpg/1280px-Statue_of_Saint_Catherine_Gravenkapel_Kortrijk_17052015_5.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -656,27 +666,27 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1364</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Saint-Denis</t>
+          <t>1374-1377</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Basilique de Saint-Denis</t>
+          <t>Chapelle des Comtes (Gravenkapel) dans l’église Notre-Dame de Courtrai</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>"Gisant de Charles V"</t>
+          <t>"Sainte Catherine"</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Marbre</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>c.195 cm</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -691,42 +701,37 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/2/21/Statue_of_Saint_Catherine_Gravenkapel_Kortrijk_17052015_5.jpg/1280px-Statue_of_Saint_Catherine_Gravenkapel_Kortrijk_17052015_5.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/b/bb/Firenze_Cattedrale_di_Santa_Maria_del_Fiore_Esterno_Lato_Nord_Portale_Timpano_2.jpg/1280px-Firenze_Cattedrale_di_Santa_Maria_del_Fiore_Esterno_Lato_Nord_Portale_Timpano_2.jpg</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>André</t>
+          <t>Giovanni</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>BEAUNEVEU</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>environ 1335</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>environ 1401</t>
+          <t>d'AMBROGIO</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1374-1377</t>
+          <t>1391-1405</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Florence</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Chapelle des Comtes (Gravenkapel) dans l’église Notre-Dame de Courtrai</t>
+          <t>Cathédrale de Florence</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>"Sainte Catherine"</t>
+          <t>"Porta della Mandorla (reliefs)"</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -734,14 +739,9 @@
           <t>Marbre</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>c.195 cm</t>
-        </is>
-      </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>française</t>
+          <t>italienne</t>
         </is>
       </c>
       <c r="U5" t="n">
@@ -751,57 +751,42 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/5/52/Tabernakel%2C_Andrea_di_Cione%2C_1359%2C_Orsanmichele_Florenz-01-185.jpg/960px-Tabernakel%2C_Andrea_di_Cione%2C_1359%2C_Orsanmichele_Florenz-01-185.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/8/82/Monument_to_Bernab%C3%B2_Visconti_%28Milan%29_01.JPG/960px-Monument_to_Bernab%C3%B2_Visconti_%28Milan%29_01.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Andrea</t>
+          <t>Bonino</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>di CIONE</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>ORCAGNA</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>ORCAGNA</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>environ 1308</t>
+          <t>da CAMPIONE</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1368</t>
+          <t>environ 1397</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1352-1359</t>
+          <t>1363</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Florence</t>
+          <t>Milan</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Église Orsanmichele</t>
+          <t>Castello Sforzesco</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>"Tabernacle marbre (protégeant la Maestà de Bernardo Daddi)"</t>
+          <t>"Tombeau de Bernabò Visconti"</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -821,52 +806,47 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/f/f6/South_Doors_of_the_Florence_Baptistry.JPG/1280px-South_Doors_of_the_Florence_Baptistry.JPG</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/a/aa/Bonino_da_Campione%2C_Arca_di_Cansignorio_%281375%29_01.jpg/960px-Bonino_da_Campione%2C_Arca_di_Cansignorio_%281375%29_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Andrea</t>
+          <t>Bonino</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>PISANO</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>environ 1290</t>
+          <t>da CAMPIONE</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1348</t>
+          <t>environ 1397</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1330-1336</t>
+          <t>1375</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Florence</t>
+          <t>Vérone</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Museo dell'Opera del Duomo</t>
+          <t>Santa Maria Antica</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>"Porte sud du Baptistère de Florence"</t>
+          <t>"Tombeau de Cansignorio della Scala"</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bronze doré</t>
+          <t>Marbre</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -881,47 +861,42 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/0/06/Andrea_pisano%2C_madonna_col_bambino_%281346_ca.%29_tra_i_ss._pietro_e_paolo_attr._a_lupo_di_francesco_%281300-30_ca.%29%2C_dalla_facciata_del_duomo_di_pisa.jpg/1280px-Andrea_pisano%2C_madonna_col_bambino_%281346_ca.%29_tra_i_ss._pietro_e_paolo_attr._a_lupo_di_francesco_%281300-30_ca.%29%2C_dalla_facciata_del_duomo_di_pisa.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/8/8d/Gisants_de_Charles_IV_le_Bel_et_Jeanne_d%27%C3%89vreux%2C_RF_1436_%26_RF_1437_%28018%29.jpg/1280px-Gisants_de_Charles_IV_le_Bel_et_Jeanne_d%27%C3%89vreux%2C_RF_1436_%26_RF_1437_%28018%29.jpg</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Andrea</t>
+          <t>Jean</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>PISANO</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>environ 1290</t>
+          <t>de LIÈGE</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1348</t>
+          <t>1381</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1346</t>
+          <t>1372</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Pise</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Cathédrale de Pise</t>
+          <t>Musée du Louvre</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>"Vierge à l'Enfant (façade de la cathédrale de Pise)"</t>
+          <t>"Gisants de Charles IV le Bel et Jeanne d'Évreux"</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -931,7 +906,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>italienne</t>
+          <t>française</t>
         </is>
       </c>
       <c r="U8" t="n">
@@ -941,47 +916,42 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/6/67/Andrea_Pisano%2C_The_Creation_of_Adam_and_Eve%2C_1334-43%2C_Museo_dell%27Opera_del_Duomo%2C_Florence.jpg/1280px-Andrea_Pisano%2C_The_Creation_of_Adam_and_Eve%2C_1334-43%2C_Museo_dell%27Opera_del_Duomo%2C_Florence.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/8/88/The_monumental_remains_of_noble_and_eminent_persons_-_comprising_the_sepulchral_antiquities_of_Great_Britain_%281826%29_%2814759570616%29.jpg/960px-The_monumental_remains_of_noble_and_eminent_persons_-_comprising_the_sepulchral_antiquities_of_Great_Britain_%281826%29_%2814759570616%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Andrea</t>
+          <t>Jean</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>PISANO</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>environ 1290</t>
+          <t>de LIÈGE</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1348</t>
+          <t>1381</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1334-1343</t>
+          <t>1366</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Florence</t>
+          <t>Londres</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Museo dell'Opera del Duomo</t>
+          <t>Westminster Abbey</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>"La Création d'Adam et Ève (relief, Campanile de Giotto)"</t>
+          <t>"Tombeau de la reine Philippa de Hainaut"</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -991,7 +961,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>italienne</t>
+          <t>française</t>
         </is>
       </c>
       <c r="U9" t="n">
@@ -1001,47 +971,62 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/8/82/Monument_to_Bernab%C3%B2_Visconti_%28Milan%29_01.JPG/960px-Monument_to_Bernab%C3%B2_Visconti_%28Milan%29_01.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/4/4d/Presentation_Scene_with_Saint_Peter_Martyr_and_Three_Donors_MET_DT4966.jpg/1280px-Presentation_Scene_with_Saint_Peter_Martyr_and_Three_Donors_MET_DT4966.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Bonino</t>
+          <t>Giovanni</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>da CAMPIONE</t>
+          <t>di BALDUCCIO</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>environ 1290</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>environ 1397</t>
+          <t>après 1349</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1363</t>
+          <t>environ 1340</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Milan</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Castello Sforzesco</t>
+          <t>Metropolitan Museum of Art</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>"Tombeau de Bernabò Visconti"</t>
+          <t>"Scène de présentation avec saint Pierre martyr et trois donateurs"</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Marbre</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>c.55 cm</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>c.87 cm</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
@@ -1056,42 +1041,47 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/a/aa/Bonino_da_Campione%2C_Arca_di_Cansignorio_%281375%29_01.jpg/960px-Bonino_da_Campione%2C_Arca_di_Cansignorio_%281375%29_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/d/d5/Tino_di_Camaino_e_aiuti%2C_sepolcro_di_Maria_di_Valois%2C_m._1331%2C_01-edit.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Bonino</t>
+          <t>Tino</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>da CAMPIONE</t>
+          <t>di CAMAINO</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>environ 1280</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>environ 1397</t>
+          <t>1337</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1375</t>
+          <t>1331</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Vérone</t>
+          <t>Naples</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Santa Maria Antica</t>
+          <t>Église Santa Chiara</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>"Tombeau de Cansignorio della Scala"</t>
+          <t>"Tombeau de Marie de Valois"</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1111,62 +1101,57 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/0/07/Well_of_Moses%2C_Champmol%2C_2010.JPG/1280px-Well_of_Moses%2C_Champmol%2C_2010.JPG</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/c/cf/Tino_di_Camaino%2C_Sepolcro_di_Riccardo_Petroni%2C_Duomo_di_Siena%2C_1315-1318.jpg/1280px-Tino_di_Camaino%2C_Sepolcro_di_Riccardo_Petroni%2C_Duomo_di_Siena%2C_1315-1318.jpg</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Claus</t>
+          <t>Tino</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>SLUTER</t>
+          <t>di CAMAINO</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>environ 1340</t>
+          <t>environ 1280</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>1405</t>
+          <t>1337</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1395-1403</t>
+          <t>1315-1318</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Sienne</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Chartreuse de Champmol</t>
+          <t>Cathédrale de Sienne</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>"Le Puits de Moïse"</t>
+          <t>"Tombeau du cardinal Riccardo Petroni"</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Pierre calcaire polychrome</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>c.4,5 m (base)</t>
+          <t>Marbre</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>néerlandaise</t>
+          <t>italienne</t>
         </is>
       </c>
       <c r="U12" t="n">
@@ -1176,57 +1161,57 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/b/b2/Dijon_Philippe_le_Hardi_Tombeau1.jpg/1280px-Dijon_Philippe_le_Hardi_Tombeau1.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/e/e5/Escultures_del_monument_f%C3%BAnebre_d%27Enric_VII%2C_Tina_di_Camaino%2C_Museo_dell%27Opera_del_Duomo%2C_Pisa.JPG/1280px-Escultures_del_monument_f%C3%BAnebre_d%27Enric_VII%2C_Tina_di_Camaino%2C_Museo_dell%27Opera_del_Duomo%2C_Pisa.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Claus</t>
+          <t>Tino</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>SLUTER</t>
+          <t>di CAMAINO</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>environ 1340</t>
+          <t>environ 1280</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1405</t>
+          <t>1337</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>1384-1410</t>
+          <t>1313-1315</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Pise</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Musée des Beaux-Arts</t>
+          <t>Museo dell'Opera del Duomo</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>"Tombeau de Philippe le Hardi"</t>
+          <t>"Statues du tombeau de l'empereur Henri VII"</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Albâtre et marbre noir</t>
+          <t>Marbre</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>néerlandaise</t>
+          <t>italienne</t>
         </is>
       </c>
       <c r="U13" t="n">
@@ -1236,57 +1221,67 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/2/29/Dijon_-_Chapelle_du_centre_hospitalier_La_Chartreuse_-_2.jpg/1280px-Dijon_-_Chapelle_du_centre_hospitalier_La_Chartreuse_-_2.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/5/52/Tabernakel%2C_Andrea_di_Cione%2C_1359%2C_Orsanmichele_Florenz-01-185.jpg/960px-Tabernakel%2C_Andrea_di_Cione%2C_1359%2C_Orsanmichele_Florenz-01-185.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Claus</t>
+          <t>Andrea</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>SLUTER</t>
+          <t>di CIONE</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>ORCAGNA</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>ORCAGNA</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>environ 1340</t>
+          <t>environ 1308</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>1405</t>
+          <t>1368</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>1393-1399</t>
+          <t>1352-1359</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Florence</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Chapelle du centre hospitalier La Chartreuse</t>
+          <t>Église Orsanmichele</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>"Porte de la chapelle"</t>
+          <t>"Tabernacle marbre (protégeant la Maestà de Bernardo Daddi)"</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Pierre</t>
+          <t>Marbre</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>néerlandaise</t>
+          <t>italienne</t>
         </is>
       </c>
       <c r="U14" t="n">
@@ -1296,37 +1291,37 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/b/bb/Firenze_Cattedrale_di_Santa_Maria_del_Fiore_Esterno_Lato_Nord_Portale_Timpano_2.jpg/1280px-Firenze_Cattedrale_di_Santa_Maria_del_Fiore_Esterno_Lato_Nord_Portale_Timpano_2.jpg</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/1b/Camposanto-tabernacole-group-museo-opera-pisa.jpg/1280px-Camposanto-tabernacole-group-museo-opera-pisa.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Giovanni</t>
+          <t>Lupo</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>d'AMBROGIO</t>
+          <t>di FRANCESCO</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>1391-1405</t>
+          <t>environ 1320</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Florence</t>
+          <t>Pise</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Cathédrale de Florence</t>
+          <t>Museo dell’opera del Duomo</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>"Porta della Mandorla (reliefs)"</t>
+          <t>"Tabernacle du Camposanto"</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -1346,62 +1341,52 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/4/4d/Presentation_Scene_with_Saint_Peter_Martyr_and_Three_Donors_MET_DT4966.jpg/1280px-Presentation_Scene_with_Saint_Peter_Martyr_and_Three_Donors_MET_DT4966.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/f/fe/Orvieto059.jpg/1280px-Orvieto059.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Giovanni</t>
+          <t>Lorenzo</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>di BALDUCCIO</t>
+          <t>MAITANI</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>environ 1290</t>
+          <t>environ 1275</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>après 1349</t>
+          <t>1330</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>environ 1340</t>
+          <t>1310-1330</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Orvieto</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Metropolitan Museum of Art</t>
+          <t>Cathédrale d'Orvieto</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>"Scène de présentation avec saint Pierre martyr et trois donateurs"</t>
+          <t>"Adam et Ève, le péché originel (relief marbre, façade)"</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Marbre</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>c.55 cm</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>c.87 cm</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
@@ -1416,57 +1401,57 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/7/77/Cathedral_pulpit_-_Pisa.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/c/cb/Busta_Petr_Parl%C3%A9%C5%99.jpg/1280px-Busta_Petr_Parl%C3%A9%C5%99.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Giovanni</t>
+          <t>Peter</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>PISANO</t>
+          <t>PARLER</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>environ 1248</t>
+          <t>1333</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>environ 1315</t>
+          <t>1399</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>1302-1310</t>
+          <t>1356-1396</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Pise</t>
+          <t>Prague</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Cathédrale de Pise</t>
+          <t>Cathédrale Saint-Guy</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>"Chaire de la cathédrale de Pise"</t>
+          <t>"Autoportrait"</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Marbre</t>
+          <t>Pierre</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>italienne</t>
+          <t>allemande</t>
         </is>
       </c>
       <c r="U17" t="n">
@@ -1476,57 +1461,57 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/3/37/Giovanni_pisano%2C_pulpito_del_duomo_di_pisa%2C_1302-11%2C_virt%C3%B9_teologali_%28fede%2C_speranza_e_carit%C3%A0%29_sulle_arti_del_trivio%2C_quadrivio_e_filosofia_03.JPG/1280px-Giovanni_pisano%2C_pulpito_del_duomo_di_pisa%2C_1302-11%2C_virt%C3%B9_teologali_%28fede%2C_speranza_e_carit%C3%A0%29_sulle_arti_del_trivio%2C_quadrivio_e_filosofia_03.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/f/fa/Prag_Dom_St._Veit_07.jpg/1280px-Prag_Dom_St._Veit_07.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Giovanni</t>
+          <t>Peter</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>PISANO</t>
+          <t>PARLER</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>environ 1248</t>
+          <t>1333</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>environ 1315</t>
+          <t>1399</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>1302-1310</t>
+          <t>1356-1396</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Pise</t>
+          <t>Prague</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Cathédrale de Pise</t>
+          <t>Cathédrale Saint-Guy</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>"Les arts libéraux, pilier central de la Chaire de la cathédrale de Pise"</t>
+          <t>"Voûtes du choeur"</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Marbre</t>
+          <t>Pierre</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>italienne</t>
+          <t>allemande</t>
         </is>
       </c>
       <c r="U18" t="n">
@@ -1536,62 +1521,52 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/f/f1/Giovanni_pisano%2C_pulpito_del_duomo_di_pisa%2C_1302-11%2C_stiloforo_02.JPG/1280px-Giovanni_pisano%2C_pulpito_del_duomo_di_pisa%2C_1302-11%2C_stiloforo_02.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/d/d1/Gisant_Robert_II_Artois_Basilique_St_Denis_St_Denis_Seine_St_Denis_1.jpg/1280px-Gisant_Robert_II_Artois_Basilique_St_Denis_St_Denis_Seine_St_Denis_1.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Giovanni</t>
+          <t>Jean</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>PISANO</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>environ 1248</t>
+          <t>PÉPIN de HUY</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>environ 1315</t>
+          <t>après 1329</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>1302-1310</t>
+          <t>environ 1320</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Pise</t>
+          <t>Saint Denis</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Cathédrale de Pise</t>
+          <t>Basilique Saint Denis</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>"Lion stylophore, Chaire de la cathédrale de Pise"</t>
+          <t>"Gisant de Robert II d’Artois"</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Marbre</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>c.90 cm</t>
+          <t>Pierre</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>italienne</t>
+          <t>française</t>
         </is>
       </c>
       <c r="U19" t="n">
@@ -1601,52 +1576,57 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/8/8d/Gisants_de_Charles_IV_le_Bel_et_Jeanne_d%27%C3%89vreux%2C_RF_1436_%26_RF_1437_%28018%29.jpg/1280px-Gisants_de_Charles_IV_le_Bel_et_Jeanne_d%27%C3%89vreux%2C_RF_1436_%26_RF_1437_%28018%29.jpg</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/f/f6/South_Doors_of_the_Florence_Baptistry.JPG/1280px-South_Doors_of_the_Florence_Baptistry.JPG</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Jean</t>
+          <t>Andrea</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>de LIÈGE</t>
+          <t>PISANO</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>environ 1290</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>1381</t>
+          <t>1348</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1372</t>
+          <t>1330-1336</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Florence</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Musée du Louvre</t>
+          <t>Museo dell'Opera del Duomo</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>"Gisants de Charles IV le Bel et Jeanne d'Évreux"</t>
+          <t>"Porte sud du Baptistère de Florence"</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Marbre</t>
+          <t>Bronze doré</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>française</t>
+          <t>italienne</t>
         </is>
       </c>
       <c r="U20" t="n">
@@ -1656,42 +1636,47 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/8/88/The_monumental_remains_of_noble_and_eminent_persons_-_comprising_the_sepulchral_antiquities_of_Great_Britain_%281826%29_%2814759570616%29.jpg/960px-The_monumental_remains_of_noble_and_eminent_persons_-_comprising_the_sepulchral_antiquities_of_Great_Britain_%281826%29_%2814759570616%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/0/06/Andrea_pisano%2C_madonna_col_bambino_%281346_ca.%29_tra_i_ss._pietro_e_paolo_attr._a_lupo_di_francesco_%281300-30_ca.%29%2C_dalla_facciata_del_duomo_di_pisa.jpg/1280px-Andrea_pisano%2C_madonna_col_bambino_%281346_ca.%29_tra_i_ss._pietro_e_paolo_attr._a_lupo_di_francesco_%281300-30_ca.%29%2C_dalla_facciata_del_duomo_di_pisa.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Jean</t>
+          <t>Andrea</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>de LIÈGE</t>
+          <t>PISANO</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>environ 1290</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>1381</t>
+          <t>1348</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>1366</t>
+          <t>1346</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Londres</t>
+          <t>Pise</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Westminster Abbey</t>
+          <t>Cathédrale de Pise</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>"Tombeau de la reine Philippa de Hainaut"</t>
+          <t>"Vierge à l'Enfant (façade de la cathédrale de Pise)"</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -1701,7 +1686,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>française</t>
+          <t>italienne</t>
         </is>
       </c>
       <c r="U21" t="n">
@@ -1711,52 +1696,57 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/d/d1/Gisant_Robert_II_Artois_Basilique_St_Denis_St_Denis_Seine_St_Denis_1.jpg/1280px-Gisant_Robert_II_Artois_Basilique_St_Denis_St_Denis_Seine_St_Denis_1.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/6/67/Andrea_Pisano%2C_The_Creation_of_Adam_and_Eve%2C_1334-43%2C_Museo_dell%27Opera_del_Duomo%2C_Florence.jpg/1280px-Andrea_Pisano%2C_The_Creation_of_Adam_and_Eve%2C_1334-43%2C_Museo_dell%27Opera_del_Duomo%2C_Florence.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Jean</t>
+          <t>Andrea</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>PÉPIN de HUY</t>
+          <t>PISANO</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>environ 1290</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>après 1329</t>
+          <t>1348</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>environ 1320</t>
+          <t>1334-1343</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Saint Denis</t>
+          <t>Florence</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Basilique Saint Denis</t>
+          <t>Museo dell'Opera del Duomo</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>"Gisant de Robert II d’Artois"</t>
+          <t>"La Création d'Adam et Ève (relief, Campanile de Giotto)"</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Pierre</t>
+          <t>Marbre</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>française</t>
+          <t>italienne</t>
         </is>
       </c>
       <c r="U22" t="n">
@@ -1766,47 +1756,47 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/f/fe/Orvieto059.jpg/1280px-Orvieto059.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/7/77/Cathedral_pulpit_-_Pisa.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Lorenzo</t>
+          <t>Giovanni</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>MAITANI</t>
+          <t>PISANO</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>environ 1275</t>
+          <t>environ 1248</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>1330</t>
+          <t>environ 1315</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>1310-1330</t>
+          <t>1302-1310</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Orvieto</t>
+          <t>Pise</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Cathédrale d'Orvieto</t>
+          <t>Cathédrale de Pise</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>"Adam et Ève, le péché originel (relief marbre, façade)"</t>
+          <t>"Chaire de la cathédrale de Pise"</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -1826,22 +1816,32 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/1b/Camposanto-tabernacole-group-museo-opera-pisa.jpg/1280px-Camposanto-tabernacole-group-museo-opera-pisa.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/3/37/Giovanni_pisano%2C_pulpito_del_duomo_di_pisa%2C_1302-11%2C_virt%C3%B9_teologali_%28fede%2C_speranza_e_carit%C3%A0%29_sulle_arti_del_trivio%2C_quadrivio_e_filosofia_03.JPG/1280px-Giovanni_pisano%2C_pulpito_del_duomo_di_pisa%2C_1302-11%2C_virt%C3%B9_teologali_%28fede%2C_speranza_e_carit%C3%A0%29_sulle_arti_del_trivio%2C_quadrivio_e_filosofia_03.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Lupo</t>
+          <t>Giovanni</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>di FRANCESCO</t>
+          <t>PISANO</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>environ 1248</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>environ 1315</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>environ 1320</t>
+          <t>1302-1310</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1851,12 +1851,12 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Museo dell’opera del Duomo</t>
+          <t>Cathédrale de Pise</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>"Tabernacle du Camposanto"</t>
+          <t>"Les arts libéraux, pilier central de la Chaire de la cathédrale de Pise"</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -1876,12 +1876,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/a/a6/Nino_pisano%2C_sibilla_eritrea%2C_1337-41%2C_dal_lato_nord_del_campanile.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/f/f1/Giovanni_pisano%2C_pulpito_del_duomo_di_pisa%2C_1302-11%2C_stiloforo_02.JPG/1280px-Giovanni_pisano%2C_pulpito_del_duomo_di_pisa%2C_1302-11%2C_stiloforo_02.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Nino</t>
+          <t>Giovanni</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1889,29 +1889,34 @@
           <t>PISANO</t>
         </is>
       </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>environ 1248</t>
+        </is>
+      </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>1368</t>
+          <t>environ 1315</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>1337-1341</t>
+          <t>1302-1310</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Florence</t>
+          <t>Pise</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Museo dell'Opera del Duomo</t>
+          <t>Cathédrale de Pise</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>"Sibylle érythréenne (relief, Campanile de Giotto)"</t>
+          <t>"Lion stylophore, Chaire de la cathédrale de Pise"</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -1936,57 +1941,57 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/c/cb/Busta_Petr_Parl%C3%A9%C5%99.jpg/1280px-Busta_Petr_Parl%C3%A9%C5%99.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/a/a6/Nino_pisano%2C_sibilla_eritrea%2C_1337-41%2C_dal_lato_nord_del_campanile.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Peter</t>
+          <t>Nino</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>PARLER</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>1333</t>
+          <t>PISANO</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>1399</t>
+          <t>1368</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>1356-1396</t>
+          <t>1337-1341</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Prague</t>
+          <t>Florence</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Cathédrale Saint-Guy</t>
+          <t>Museo dell'Opera del Duomo</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>"Autoportrait"</t>
+          <t>"Sibylle érythréenne (relief, Campanile de Giotto)"</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Pierre</t>
+          <t>Marbre</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>c.90 cm</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>allemande</t>
+          <t>italienne</t>
         </is>
       </c>
       <c r="U26" t="n">
@@ -1996,57 +2001,62 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/f/fa/Prag_Dom_St._Veit_07.jpg/1280px-Prag_Dom_St._Veit_07.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/0/07/Well_of_Moses%2C_Champmol%2C_2010.JPG/1280px-Well_of_Moses%2C_Champmol%2C_2010.JPG</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Peter</t>
+          <t>Claus</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>PARLER</t>
+          <t>SLUTER</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>1333</t>
+          <t>environ 1340</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>1399</t>
+          <t>1405</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>1356-1396</t>
+          <t>1395-1403</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Prague</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Cathédrale Saint-Guy</t>
+          <t>Chartreuse de Champmol</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>"Voûtes du choeur"</t>
+          <t>"Le Puits de Moïse"</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Pierre</t>
+          <t>Pierre calcaire polychrome</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>c.4,5 m (base)</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>allemande</t>
+          <t>néerlandaise</t>
         </is>
       </c>
       <c r="U27" t="n">
@@ -2056,57 +2066,57 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/d/d5/Tino_di_Camaino_e_aiuti%2C_sepolcro_di_Maria_di_Valois%2C_m._1331%2C_01-edit.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/b/b2/Dijon_Philippe_le_Hardi_Tombeau1.jpg/1280px-Dijon_Philippe_le_Hardi_Tombeau1.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Tino</t>
+          <t>Claus</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>di CAMAINO</t>
+          <t>SLUTER</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>environ 1280</t>
+          <t>environ 1340</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>1337</t>
+          <t>1405</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>1331</t>
+          <t>1384-1410</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Naples</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Église Santa Chiara</t>
+          <t>Musée des Beaux-Arts</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>"Tombeau de Marie de Valois"</t>
+          <t>"Tombeau de Philippe le Hardi"</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Marbre</t>
+          <t>Albâtre et marbre noir</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>italienne</t>
+          <t>néerlandaise</t>
         </is>
       </c>
       <c r="U28" t="n">
@@ -2116,57 +2126,57 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/c/cf/Tino_di_Camaino%2C_Sepolcro_di_Riccardo_Petroni%2C_Duomo_di_Siena%2C_1315-1318.jpg/1280px-Tino_di_Camaino%2C_Sepolcro_di_Riccardo_Petroni%2C_Duomo_di_Siena%2C_1315-1318.jpg</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/2/29/Dijon_-_Chapelle_du_centre_hospitalier_La_Chartreuse_-_2.jpg/1280px-Dijon_-_Chapelle_du_centre_hospitalier_La_Chartreuse_-_2.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Tino</t>
+          <t>Claus</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>di CAMAINO</t>
+          <t>SLUTER</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>environ 1280</t>
+          <t>environ 1340</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>1337</t>
+          <t>1405</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>1315-1318</t>
+          <t>1393-1399</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Sienne</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Cathédrale de Sienne</t>
+          <t>Chapelle du centre hospitalier La Chartreuse</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>"Tombeau du cardinal Riccardo Petroni"</t>
+          <t>"Porte de la chapelle"</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Marbre</t>
+          <t>Pierre</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>italienne</t>
+          <t>néerlandaise</t>
         </is>
       </c>
       <c r="U29" t="n">
@@ -2176,47 +2186,37 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/e/e5/Escultures_del_monument_f%C3%BAnebre_d%27Enric_VII%2C_Tina_di_Camaino%2C_Museo_dell%27Opera_del_Duomo%2C_Pisa.JPG/1280px-Escultures_del_monument_f%C3%BAnebre_d%27Enric_VII%2C_Tina_di_Camaino%2C_Museo_dell%27Opera_del_Duomo%2C_Pisa.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/e/eb/Agnolo_di_ventura%2C_portale_della_cappella_petroni%2C_1336%2C_02_madonna_col_bambino_tra_s._francesco_e_il_beato_pietro_da_siena.jpg/1280px-Agnolo_di_ventura%2C_portale_della_cappella_petroni%2C_1336%2C_02_madonna_col_bambino_tra_s._francesco_e_il_beato_pietro_da_siena.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Tino</t>
+          <t>Agnolo</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>di CAMAINO</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>environ 1280</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>1337</t>
+          <t>VENTURA</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>1313-1315</t>
+          <t>1336</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Pise</t>
+          <t>Sienne</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Museo dell'Opera del Duomo</t>
+          <t>Basilique San Francesco</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>"Statues du tombeau de l'empereur Henri VII"</t>
+          <t>"Portail de la chapelle Petroni"</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">

--- a/quizzes/sculpture-14e.xlsx
+++ b/quizzes/sculpture-14e.xlsx
@@ -577,7 +577,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>environ 1377</t>
+          <t>1377 environ</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -632,12 +632,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>environ 1335</t>
+          <t>1335 environ</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>environ 1401</t>
+          <t>1401 environ</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -692,12 +692,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>environ 1335</t>
+          <t>1335 environ</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>environ 1401</t>
+          <t>1401 environ</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -802,7 +802,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>environ 1397</t>
+          <t>1397 environ</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>environ 1397</t>
+          <t>1397 environ</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>environ 1290</t>
+          <t>1290 environ</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>environ 1340</t>
+          <t>1340 environ</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>environ 1280</t>
+          <t>1280 environ</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>environ 1280</t>
+          <t>1280 environ</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1212,7 +1212,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>environ 1280</t>
+          <t>1280 environ</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1282,7 +1282,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>environ 1308</t>
+          <t>1308 environ</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>environ 1320</t>
+          <t>1320 environ</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>environ 1275</t>
+          <t>1275 environ</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1577,7 +1577,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>environ 1320</t>
+          <t>1320 environ</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1627,7 +1627,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>environ 1290</t>
+          <t>1290 environ</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1687,7 +1687,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>environ 1290</t>
+          <t>1290 environ</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1747,7 +1747,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>environ 1290</t>
+          <t>1290 environ</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1807,12 +1807,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>environ 1248</t>
+          <t>1248 environ</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>environ 1315</t>
+          <t>1315 environ</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1867,12 +1867,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>environ 1248</t>
+          <t>1248 environ</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>environ 1315</t>
+          <t>1315 environ</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1927,12 +1927,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>environ 1248</t>
+          <t>1248 environ</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>environ 1315</t>
+          <t>1315 environ</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>environ 1340</t>
+          <t>1340 environ</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2112,7 +2112,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>environ 1340</t>
+          <t>1340 environ</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -2172,7 +2172,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>environ 1340</t>
+          <t>1340 environ</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
